--- a/tool/track-aggregator/doc/03_結合テスト/test-data/clients/ok-2025.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/test-data/clients/ok-2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\clients\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\test-data\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C6B527-6A18-4162-BB08-E3D4B467BD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF61660-C425-493C-A529-2F7F050DCDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
   <sheets>
     <sheet name="受講生一覧" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -63,15 +63,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>Web技術入門</t>
-  </si>
-  <si>
-    <t>Javaプログラミング基礎</t>
-  </si>
-  <si>
-    <t>開発プロセス</t>
-  </si>
-  <si>
     <t>テスト名</t>
     <rPh sb="3" eb="4">
       <t>メイ</t>
@@ -99,75 +90,6 @@
   </si>
   <si>
     <t>社会を支えるITサービス</t>
-  </si>
-  <si>
-    <t>アルゴリズム入門</t>
-  </si>
-  <si>
-    <t>49081-645551</t>
-  </si>
-  <si>
-    <t>データベース技術入門</t>
-  </si>
-  <si>
-    <t>Javaプログラミング応用</t>
-  </si>
-  <si>
-    <t>サービスデザイン</t>
-  </si>
-  <si>
-    <t>48693-639607</t>
-  </si>
-  <si>
-    <t>テクニカル総合演習</t>
-  </si>
-  <si>
-    <t>ビジネス基礎</t>
-  </si>
-  <si>
-    <t>ビジネス応用</t>
-  </si>
-  <si>
-    <t>49080-645520,49081-645551,49082-645582,49083-645613</t>
-  </si>
-  <si>
-    <t>48692-639579,48702-639819,48745-640773,48782-641366</t>
-  </si>
-  <si>
-    <t>48694-639641,48704-639881,48747-640835,48784-641428</t>
-  </si>
-  <si>
-    <t>48699-639759,48709-639999,48779-641306,48789-641546</t>
-  </si>
-  <si>
-    <t>48698-639742,48708-639982,48778-641289,48788-641529</t>
-  </si>
-  <si>
-    <t>49080-645523,49081-645554,49082-645585,49083-645616</t>
-  </si>
-  <si>
-    <t>48692-639582,48702-639822,48745-640776,48782-641369</t>
-  </si>
-  <si>
-    <t>48694-639644,48704-639884,48747-640838,48784-641431</t>
-  </si>
-  <si>
-    <t>48696-639724,48706-639964,48776-641271,48786-641511</t>
-  </si>
-  <si>
-    <t>48699-639762,48709-640002,48779-641309,48789-641549</t>
-  </si>
-  <si>
-    <t>48698-639745,48708-639985,48778-641292,48788-641532</t>
-  </si>
-  <si>
-    <t>48697-639725,48707-639965,48777-641272,48787-641512</t>
-  </si>
-  <si>
-    <t>48497-637400,48502-637419,48507-637439,48512-637458</t>
-  </si>
-  <si>
-    <t>48499-637402,48504-637422,48509-637441,48514-637460</t>
   </si>
   <si>
     <t>49080-645520</t>
@@ -1241,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>4</v>
@@ -1252,13 +1174,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -1273,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CC9836-71F6-4801-9ED5-83CF14DFE1E5}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -1285,13 +1207,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D1" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
@@ -1302,118 +1224,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1424,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24723F39-5800-40B8-82C1-AF1FD4F94096}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -1436,13 +1256,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
@@ -1453,186 +1273,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
